--- a/data/2026/Grocery 2026/cleaned/sale_feb_26_cleaned.xlsx
+++ b/data/2026/Grocery 2026/cleaned/sale_feb_26_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,2906 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>003742P</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GODREJ CREAM HAIR COL BROWN</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33</v>
+      </c>
+      <c r="K2" t="n">
+        <v>700.26</v>
+      </c>
+      <c r="L2" t="n">
+        <v>666.9299999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43</v>
+      </c>
+      <c r="O2" t="n">
+        <v>78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>009682A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9682</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PARACHUTE JASMINE HAIR OIL 300 ML</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>76.45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>481.62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="N3" t="n">
+        <v>129</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>004061D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4061</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T/PASTE CLOSE UP 150 GMS RED</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1680.26</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1600.22</v>
+      </c>
+      <c r="M4" t="n">
+        <v>80.04000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>009951U</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9951</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WHISPER ULTRA CEAN XL WING 30 S</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>212.09</v>
+      </c>
+      <c r="G5" t="n">
+        <v>222.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6680.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6362.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>318</v>
+      </c>
+      <c r="N5" t="n">
+        <v>104</v>
+      </c>
+      <c r="O5" t="n">
+        <v>58</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>009414T</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T/POWDER YARDLY 200GMS</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1007.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>959.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>97</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>004987A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUNSILK SHAMPOO 180 ML LUSCIOUSLY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>72.58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2758.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2626.56</v>
+      </c>
+      <c r="M7" t="n">
+        <v>131.48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>95</v>
+      </c>
+      <c r="O7" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>007081N</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NATURAL RACHNI MAHANDI 250G</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1816.27</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1729.85</v>
+      </c>
+      <c r="M8" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="N8" t="n">
+        <v>104</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>008633T</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8633</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NEXT SILVER NO GAS PERFUME 120ML</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>181.97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5641.07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5372.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>268.77</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>51</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>009038Y</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9038</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SOAP MARGO 100 GMS</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>009813H</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9813</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PAMPER ACTIVE BABY 32XL</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>578.88</v>
+      </c>
+      <c r="G11" t="n">
+        <v>607.8200000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21273.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20260.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1012.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>72</v>
+      </c>
+      <c r="O11" t="n">
+        <v>96</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>001212D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>A/S LOTION PARK AV  50ML</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16</v>
+      </c>
+      <c r="O12" t="n">
+        <v>70</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>009442L</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9442</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AXE DENIM POWDER BLACK 300M</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1820.07</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1733.34</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="N13" t="n">
+        <v>38</v>
+      </c>
+      <c r="O13" t="n">
+        <v>49</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>008806H</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SOAP HIMLAYA NEEM 75 GMS</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>41</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>009660D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H/OIL SHANTI AMLA 300ML</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>48</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2689.44</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2561.28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>128.16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>126</v>
+      </c>
+      <c r="O15" t="n">
+        <v>74</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>005298A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HEAD SHOULDER ANTI 675 ML</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>361.26</v>
+      </c>
+      <c r="G16" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="H16" t="n">
+        <v>63</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>63</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23897.16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22759.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1137.78</v>
+      </c>
+      <c r="N16" t="n">
+        <v>104</v>
+      </c>
+      <c r="O16" t="n">
+        <v>31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>007209I</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7209</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INSIGHT JEWEL LIQ SINDOOR 9ML</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>73.41</v>
+      </c>
+      <c r="G17" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1849.92</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1761.84</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>71</v>
+      </c>
+      <c r="O17" t="n">
+        <v>18</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>004102A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COLGATE CHARCOAL CLEAN TOOTHPASTE</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="G18" t="n">
+        <v>110.39</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1324.68</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1261.56</v>
+      </c>
+      <c r="M18" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>36</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>004100F</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>T/PASTE EMOFORM 100G</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>432.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>80</v>
+      </c>
+      <c r="O19" t="n">
+        <v>81</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>009267H</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9267</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>W/POWDER HENKO 3 KG</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="G20" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3313.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3216.8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>147</v>
+      </c>
+      <c r="O20" t="n">
+        <v>43</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>021821K</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>21821</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SUNFLAME GYSSER 25L</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6682.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6749.58</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26998.32</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26731</v>
+      </c>
+      <c r="M21" t="n">
+        <v>267.32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>49</v>
+      </c>
+      <c r="O21" t="n">
+        <v>73</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>013189S</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>13189</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SUPERFLAME PEARL P/COOKER 3 LTR</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>933.24</v>
+      </c>
+      <c r="G22" t="n">
+        <v>979.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5879.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5599.44</v>
+      </c>
+      <c r="M22" t="n">
+        <v>279.96</v>
+      </c>
+      <c r="N22" t="n">
+        <v>87</v>
+      </c>
+      <c r="O22" t="n">
+        <v>71</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>017192L</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>17192</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DABUR MULTI SURFACE CL 150GM</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>113.08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>949.84</v>
+      </c>
+      <c r="L23" t="n">
+        <v>904.64</v>
+      </c>
+      <c r="M23" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>128</v>
+      </c>
+      <c r="O23" t="n">
+        <v>55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>020978A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>C/FAN BAJAJ GRACE HS 48" BROWN</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1955.61</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2053.39</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13</v>
+      </c>
+      <c r="K24" t="n">
+        <v>26694.07</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25422.93</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1271.14</v>
+      </c>
+      <c r="N24" t="n">
+        <v>72</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>027065P</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>27065</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HARPIC BATH ROOM CLENER</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="G25" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>899.7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21</v>
+      </c>
+      <c r="O25" t="n">
+        <v>58</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>013203B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13203</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BAJAJ HANDI ANODIZED3L PCN X 63 H</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1523.44</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1599.61</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" t="n">
+        <v>38390.64</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36562.56</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1828.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>141</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>018580K</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>18580</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>KUSHAL CLEANWRAP ALUNINIUM 9MT DISP</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="G27" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>129.76</v>
+      </c>
+      <c r="L27" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="N27" t="n">
+        <v>110</v>
+      </c>
+      <c r="O27" t="n">
+        <v>79</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>021147J</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21147</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SUMMER COOL MIXER JUCIER GRINDER</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2784.59</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2923.82</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>11695.28</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11138.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>556.92</v>
+      </c>
+      <c r="N28" t="n">
+        <v>102</v>
+      </c>
+      <c r="O28" t="n">
+        <v>24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>021348S</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21348</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IMERS/HEATER SUNFLAME 1KW</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="G29" t="n">
+        <v>405.03</v>
+      </c>
+      <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6885.51</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6557.58</v>
+      </c>
+      <c r="M29" t="n">
+        <v>327.93</v>
+      </c>
+      <c r="N29" t="n">
+        <v>52</v>
+      </c>
+      <c r="O29" t="n">
+        <v>44</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>027360E</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27360</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MIRROR PAM -112</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="G30" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="H30" t="n">
+        <v>42</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>42</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1347.36</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1283.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="N30" t="n">
+        <v>75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>95</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>027181X</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>27181</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MOSKIOUT REFILL 45 ML</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="G31" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" t="n">
+        <v>557.83</v>
+      </c>
+      <c r="L31" t="n">
+        <v>531.3099999999999</v>
+      </c>
+      <c r="M31" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="N31" t="n">
+        <v>86</v>
+      </c>
+      <c r="O31" t="n">
+        <v>57</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>027027E</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EXO DISH WASH BAR 300G</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>60</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1029</v>
+      </c>
+      <c r="L32" t="n">
+        <v>979.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>131</v>
+      </c>
+      <c r="O32" t="n">
+        <v>65</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>041398S</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>41398</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SAGAR SOFT FEEL BRA 34'</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>120.51</v>
+      </c>
+      <c r="G33" t="n">
+        <v>126.54</v>
+      </c>
+      <c r="H33" t="n">
+        <v>75</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>75</v>
+      </c>
+      <c r="K33" t="n">
+        <v>9490.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9038.25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>452.25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>112</v>
+      </c>
+      <c r="O33" t="n">
+        <v>36</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>048462H</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>48462</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ADIDAS GALACTUS SHOES 8 SIZ</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2274.17</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2387.88</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>57309.12</v>
+      </c>
+      <c r="L34" t="n">
+        <v>54580.08</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2729.04</v>
+      </c>
+      <c r="N34" t="n">
+        <v>133</v>
+      </c>
+      <c r="O34" t="n">
+        <v>91</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>037258G</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>37258</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NUVALDO PLUS 70</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3217.87</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3378.76</v>
+      </c>
+      <c r="H35" t="n">
+        <v>20</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>67575.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>64357.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3217.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>117</v>
+      </c>
+      <c r="O35" t="n">
+        <v>24</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>034035C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>34035</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NEW SITI PLASTIC MUGG 1LTR</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="H36" t="n">
+        <v>48</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>48</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1034.88</v>
+      </c>
+      <c r="L36" t="n">
+        <v>985.4400000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="N36" t="n">
+        <v>105</v>
+      </c>
+      <c r="O36" t="n">
+        <v>79</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>041291K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>41291</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VIP ULTRA TRUNK 90 CM</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>113.17</v>
+      </c>
+      <c r="G37" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="H37" t="n">
+        <v>31</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>29</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3446.07</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3281.93</v>
+      </c>
+      <c r="M37" t="n">
+        <v>164.14</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>042016A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SOCKS ADIDAS BL/WH/GREY</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="G38" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="H38" t="n">
+        <v>13</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>13</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1792.96</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1707.55</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>037251P</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>37251</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SAFARI REPLAY 60 SOFT LUGGAGE</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2386.47</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2505.79</v>
+      </c>
+      <c r="H39" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>13</v>
+      </c>
+      <c r="K39" t="n">
+        <v>32575.27</v>
+      </c>
+      <c r="L39" t="n">
+        <v>31024.11</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1551.16</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>086073T</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>86073</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TEA D/ DIAMOND 1 KG</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="G40" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="H40" t="n">
+        <v>32</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>32</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10942.72</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10834.24</v>
+      </c>
+      <c r="M40" t="n">
+        <v>108.48</v>
+      </c>
+      <c r="N40" t="n">
+        <v>80</v>
+      </c>
+      <c r="O40" t="n">
+        <v>34</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>085626D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>85626</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NAMKIN ALU BHUJIA BIKANO</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>24</v>
+      </c>
+      <c r="K41" t="n">
+        <v>783.12</v>
+      </c>
+      <c r="L41" t="n">
+        <v>745.92</v>
+      </c>
+      <c r="M41" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>11</v>
+      </c>
+      <c r="O41" t="n">
+        <v>23</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>085036F</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>85036</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MCVI TIES DIGESTIVE BIS 100G</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="G42" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="H42" t="n">
+        <v>26</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>26</v>
+      </c>
+      <c r="K42" t="n">
+        <v>458.38</v>
+      </c>
+      <c r="L42" t="n">
+        <v>436.54</v>
+      </c>
+      <c r="M42" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="n">
+        <v>65</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>085081Y</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>85081</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BISC.KRACK JACK 75 GM</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H43" t="n">
+        <v>29</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>29</v>
+      </c>
+      <c r="K43" t="n">
+        <v>140.65</v>
+      </c>
+      <c r="L43" t="n">
+        <v>133.98</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N43" t="n">
+        <v>39</v>
+      </c>
+      <c r="O43" t="n">
+        <v>31</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>086307L</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>86307</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BADSHAH HOT CHICKEN MASALA</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="G44" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="H44" t="n">
+        <v>39</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>39</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1865.37</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1776.45</v>
+      </c>
+      <c r="M44" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="N44" t="n">
+        <v>140</v>
+      </c>
+      <c r="O44" t="n">
+        <v>33</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>085481X</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>85481</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>REAL LITCH 1 LTR</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="G45" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="H45" t="n">
+        <v>12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" t="n">
+        <v>965.04</v>
+      </c>
+      <c r="L45" t="n">
+        <v>919.08</v>
+      </c>
+      <c r="M45" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="N45" t="n">
+        <v>97</v>
+      </c>
+      <c r="O45" t="n">
+        <v>54</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>085792A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>85792</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GULAB JAMUN HALDIRAM</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>151.31</v>
+      </c>
+      <c r="G46" t="n">
+        <v>158.88</v>
+      </c>
+      <c r="H46" t="n">
+        <v>25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3972</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3782.75</v>
+      </c>
+      <c r="M46" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>64</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>085375L</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FROOTI GREEN MANGO 1L</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="G47" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="H47" t="n">
+        <v>16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>16</v>
+      </c>
+      <c r="K47" t="n">
+        <v>743.2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>707.84</v>
+      </c>
+      <c r="M47" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="N47" t="n">
+        <v>132</v>
+      </c>
+      <c r="O47" t="n">
+        <v>46</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>084973H</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>84973</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BIS PRIYA GOLD SNACKS ZIG ZAG</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>27</v>
+      </c>
+      <c r="L48" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N48" t="n">
+        <v>102</v>
+      </c>
+      <c r="O48" t="n">
+        <v>31</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>085066A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>85066</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DUKES DIGESTIVE NATURAL GOODNESS</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="H49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>10</v>
+      </c>
+      <c r="K49" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="N49" t="n">
+        <v>54</v>
+      </c>
+      <c r="O49" t="n">
+        <v>78</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>086152T</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>86152</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MARVEL GOLD TEA 1KG</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="G50" t="n">
+        <v>312.21</v>
+      </c>
+      <c r="H50" t="n">
+        <v>31</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>31</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9678.51</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9582.719999999999</v>
+      </c>
+      <c r="M50" t="n">
+        <v>95.79000000000001</v>
+      </c>
+      <c r="N50" t="n">
+        <v>42</v>
+      </c>
+      <c r="O50" t="n">
+        <v>61</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>085353A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BAMBINO TOMATO SOUP</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="G51" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="H51" t="n">
+        <v>41</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>41</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1298.06</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1236.15</v>
+      </c>
+      <c r="M51" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="N51" t="n">
+        <v>112</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
